--- a/databases/tabela_contingencia_sus.xlsx
+++ b/databases/tabela_contingencia_sus.xlsx
@@ -382,14 +382,20 @@
           <t>Highest rates</t>
         </is>
       </c>
-      <c r="B2">
-        <v>71</v>
-      </c>
-      <c r="C2">
-        <v>552</v>
-      </c>
-      <c r="D2">
-        <v>1841</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>349 (6.3%)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>418 (7.5%)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>129 (2.3%)</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -398,14 +404,20 @@
           <t>Intermediary rates</t>
         </is>
       </c>
-      <c r="B3">
-        <v>212</v>
-      </c>
-      <c r="C3">
-        <v>1145</v>
-      </c>
-      <c r="D3">
-        <v>853</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>242 (4.3%)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1240 (22.3%)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>728 (13.1%)</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -414,14 +426,20 @@
           <t>Lowest rates</t>
         </is>
       </c>
-      <c r="B4">
-        <v>325</v>
-      </c>
-      <c r="C4">
-        <v>423</v>
-      </c>
-      <c r="D4">
-        <v>148</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>77 (1.4%)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>649 (11.7%)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1738 (31.2%)</t>
+        </is>
       </c>
     </row>
   </sheetData>
